--- a/experiment_output/OneCombinedGame/ElapsedTimePerFilesSetOfSevenOneCombinedGameFinal.xlsx
+++ b/experiment_output/OneCombinedGame/ElapsedTimePerFilesSetOfSevenOneCombinedGameFinal.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\90948045\OneDrive - Western Sydney University\Documents\ThesisTimingData\OneCombinedGame\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://westernsydneyedu-my.sharepoint.com/personal/90948045_westernsydney_edu_au/Documents/Documents/Thesis/OneCombinedGame/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A26BD5EB-0394-4EC2-8D90-F5DB4911E2E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="39" documentId="13_ncr:1_{A26BD5EB-0394-4EC2-8D90-F5DB4911E2E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{62D1BC45-51D0-4AAB-91E0-7A0D769F2F49}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="11964" xr2:uid="{B1AA7F2C-2C73-4090-B4EC-3BCDF56883FD}"/>
   </bookViews>
@@ -5184,7 +5184,10 @@
   <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="5" width="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.33203125" customWidth="1"/>
+    <col min="2" max="2" width="9.44140625" customWidth="1"/>
+    <col min="3" max="3" width="9" customWidth="1"/>
+    <col min="4" max="5" width="9.109375" customWidth="1"/>
     <col min="6" max="6" width="13.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5309,9 +5312,14 @@
   <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="5" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.44140625" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" customWidth="1"/>
+    <col min="3" max="3" width="9.5546875" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" customWidth="1"/>
     <col min="6" max="6" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.6640625" customWidth="1"/>
+    <col min="8" max="8" width="9.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
